--- a/artfynd/A 16171-2023 artfynd.xlsx
+++ b/artfynd/A 16171-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16171-2023 artfynd.xlsx
+++ b/artfynd/A 16171-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17176503</v>
+        <v>131886179</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia ferruginosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(J.F.Gmel.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rälla hed-St. Rör ost väg 136, Öl</t>
+          <t>Rönnerum, Väg 136  Isgärde, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595138.0257879844</v>
+        <v>595492</v>
       </c>
       <c r="R2" t="n">
-        <v>6290876.755286385</v>
+        <v>6290771</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-03-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-03-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På död stående hassel.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,76 +762,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>hassel och tall på lite fuktigare sandmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Heléne Wertwein Haavikko</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Heléne Wertwein Haavikko</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64823201</v>
+        <v>64823483</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>206046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rosti ost, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595219.1489462625</v>
+        <v>595137</v>
       </c>
       <c r="R3" t="n">
-        <v>6290789.205051713</v>
+        <v>6290953</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,19 +857,9 @@
           <t>2017-04-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64823210</v>
+        <v>17176500</v>
       </c>
       <c r="B4" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,16 +897,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,14 +920,14 @@
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rosti ost, Öl</t>
+          <t>Rälla hed-St. Rör ost v. 136, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595219.1489462625</v>
+        <v>595200</v>
       </c>
       <c r="R4" t="n">
-        <v>6290789.205051713</v>
+        <v>6291078</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-04-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +973,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>hässle med tall och skogsek</t>
+          <t>hassel och tall på lite fuktigare sandmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,7 +987,450 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64823201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rosti ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595219</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6290789</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>64823210</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111389</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rosti ost, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595219</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6290789</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-04-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>hässle med tall och skogsek</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17176503</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rälla hed-St. Rör ost väg 136, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595138</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6290877</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>hassel och tall på lite fuktigare sandmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>17176505</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106385</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224190</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Flockarun</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Centaurium erythraea var. erythraea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rälla hed-St. Rör ost väg 136, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595080</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6290906</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsrum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-03-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16171-2023 artfynd.xlsx
+++ b/artfynd/A 16171-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131886179</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64823483</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17176500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64823201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64823210</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17176503</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,8 +1466,22 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17176505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>